--- a/config/demo/forms/contact/person-create.xlsx
+++ b/config/demo/forms/contact/person-create.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR50"/>
+  <dimension ref="A1:AR53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.44140625" customWidth="1" min="1" max="1"/>
@@ -1020,54 +1020,46 @@
       <c r="AR6" s="12" t="n"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="V7" s="12" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="12" t="n"/>
-      <c r="Y7" s="12" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="12" t="n"/>
-      <c r="AB7" s="12" t="n"/>
-      <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="12" t="n"/>
-      <c r="AE7" s="12" t="n"/>
-      <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="12" t="n"/>
-      <c r="AH7" s="12" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="12" t="n"/>
-      <c r="AK7" s="12" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="12" t="n"/>
-      <c r="AN7" s="12" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="12" t="n"/>
-      <c r="AQ7" s="12" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Role of the logged in user</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>लॉग इन यूज़र की भूमिका</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Peran dari login user</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jukumu la mtumizi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>लग इन गरेको प्रयोगकर्ताको भूमिका</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Rôle de l'utilisateur connecté</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -1122,45 +1114,17 @@
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>init</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
@@ -1184,11 +1148,7 @@
       <c r="AD9" s="12" t="n"/>
       <c r="AE9" s="12" t="n"/>
       <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="inlineStr">
-        <is>
-          <t>Cannot be inside the person group without having all fields saved to person. And needs separate db-objects because cannot have one that handles the different place types. Last part is now incorrect... as long as it is read only it could be a string of appearance db-object and work fine.</t>
-        </is>
-      </c>
+      <c r="AG9" s="12" t="n"/>
       <c r="AH9" s="12" t="n"/>
       <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="12" t="n"/>
@@ -1204,57 +1164,49 @@
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>parent_id</t>
+          <t>init</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Belongs To</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>यह व्यक्ति इस जगह से जुड़ा है</t>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Orang ini terhubung ke tempat ini</t>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Ni wa</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>यो व्यक्ति यस ठाउँसँग सम्बन्धित छ</t>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Associé avec</t>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>select-contact</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
       <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="12" t="n"/>
@@ -1263,46 +1215,22 @@
       <c r="S10" s="12" t="n"/>
       <c r="T10" s="12" t="n"/>
       <c r="U10" s="12" t="n"/>
-      <c r="V10" s="12" t="inlineStr">
-        <is>
-          <t>${parent}</t>
-        </is>
-      </c>
+      <c r="V10" s="12" t="n"/>
       <c r="W10" s="12" t="n"/>
-      <c r="X10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
-      <c r="Y10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
-      <c r="Z10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
-      <c r="AA10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
-      <c r="AB10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
+      <c r="X10" s="12" t="n"/>
+      <c r="Y10" s="12" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="12" t="n"/>
+      <c r="AB10" s="12" t="n"/>
       <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="12" t="inlineStr">
-        <is>
-          <t>${type_label}</t>
-        </is>
-      </c>
+      <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="12" t="n"/>
       <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
+      <c r="AG10" s="12" t="inlineStr">
+        <is>
+          <t>Cannot be inside the person group without having all fields saved to person. And needs separate db-objects because cannot have one that handles the different place types. Last part is now incorrect... as long as it is read only it could be a string of appearance db-object and work fine.</t>
+        </is>
+      </c>
       <c r="AH10" s="12" t="n"/>
       <c r="AI10" s="12" t="n"/>
       <c r="AJ10" s="12" t="n"/>
@@ -1323,48 +1251,52 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>parent_id</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
+          <t>Belongs To</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>यह व्यक्ति इस जगह से जुड़ा है</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
+          <t>Orang ini terhubung ke tempat ini</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
+          <t>Ni wa</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>यो व्यक्ति यस ठाउँसँग सम्बन्धित छ</t>
         </is>
       </c>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
+          <t>Associé avec</t>
         </is>
       </c>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="n"/>
+          <t>select-contact</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="12" t="n"/>
@@ -1373,15 +1305,43 @@
       <c r="S11" s="12" t="n"/>
       <c r="T11" s="12" t="n"/>
       <c r="U11" s="12" t="n"/>
-      <c r="V11" s="12" t="n"/>
+      <c r="V11" s="12" t="inlineStr">
+        <is>
+          <t>${parent}</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="n"/>
-      <c r="X11" s="12" t="n"/>
-      <c r="Y11" s="12" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="12" t="n"/>
-      <c r="AB11" s="12" t="n"/>
+      <c r="X11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
+      <c r="Y11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
+      <c r="Z11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
       <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="12" t="n"/>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>${type_label}</t>
+        </is>
+      </c>
       <c r="AE11" s="12" t="n"/>
       <c r="AF11" s="12" t="n"/>
       <c r="AG11" s="12" t="n"/>
@@ -1405,7 +1365,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1482,12 +1442,12 @@
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>select_one place_type</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>type_selector</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1537,11 +1497,7 @@
       <c r="S13" s="12" t="n"/>
       <c r="T13" s="12" t="n"/>
       <c r="U13" s="12" t="n"/>
-      <c r="V13" s="14" t="inlineStr">
-        <is>
-          <t>../type</t>
-        </is>
-      </c>
+      <c r="V13" s="12" t="n"/>
       <c r="W13" s="12" t="n"/>
       <c r="X13" s="12" t="n"/>
       <c r="Y13" s="12" t="n"/>
@@ -1568,24 +1524,52 @@
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one place_type</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>type_label</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
+          <t>type_selector</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
       <c r="M14" s="12" t="n"/>
       <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
@@ -1595,9 +1579,9 @@
       <c r="S14" s="12" t="n"/>
       <c r="T14" s="12" t="n"/>
       <c r="U14" s="12" t="n"/>
-      <c r="V14" s="12" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${type_selector},'${type_selector}')</t>
+      <c r="V14" s="14" t="inlineStr">
+        <is>
+          <t>../type</t>
         </is>
       </c>
       <c r="W14" s="12" t="n"/>
@@ -1626,10 +1610,14 @@
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>type_label</t>
+        </is>
+      </c>
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
@@ -1649,7 +1637,11 @@
       <c r="S15" s="12" t="n"/>
       <c r="T15" s="12" t="n"/>
       <c r="U15" s="12" t="n"/>
-      <c r="V15" s="12" t="n"/>
+      <c r="V15" s="12" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${type_selector},'${type_selector}')</t>
+        </is>
+      </c>
       <c r="W15" s="12" t="n"/>
       <c r="X15" s="12" t="n"/>
       <c r="Y15" s="12" t="n"/>
@@ -1674,140 +1666,116 @@
       <c r="AR15" s="12" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="17" t="n"/>
-      <c r="S16" s="18" t="n"/>
-      <c r="T16" s="19" t="n"/>
-      <c r="U16" s="29" t="n"/>
-      <c r="Y16" s="15" t="n"/>
-      <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="17" t="n"/>
-      <c r="AB16" s="18" t="n"/>
-      <c r="AC16" s="19" t="n"/>
-      <c r="AD16" s="29" t="n"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="12" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="12" t="n"/>
+      <c r="Y16" s="12" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="12" t="n"/>
+      <c r="AB16" s="12" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="12" t="n"/>
+      <c r="AK16" s="12" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="12" t="n"/>
+      <c r="AN16" s="12" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="12" t="n"/>
+      <c r="AQ16" s="12" t="n"/>
+      <c r="AR16" s="12" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="C17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="E17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="G17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="29" t="n"/>
-      <c r="O17" s="29" t="n"/>
-      <c r="P17" s="29" t="n"/>
-      <c r="Q17" s="29" t="n"/>
-      <c r="R17" s="29" t="n"/>
-      <c r="S17" s="29" t="n"/>
-      <c r="T17" s="29" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="29" t="n"/>
+      <c r="O17" s="21" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="17" t="n"/>
+      <c r="S17" s="18" t="n"/>
+      <c r="T17" s="19" t="n"/>
       <c r="U17" s="29" t="n"/>
-      <c r="V17" s="29" t="n"/>
-      <c r="W17" s="29" t="n"/>
-      <c r="X17" s="29" t="n"/>
-      <c r="Y17" s="29" t="n"/>
-      <c r="Z17" s="29" t="n"/>
-      <c r="AA17" s="29" t="n"/>
-      <c r="AB17" s="29" t="n"/>
-      <c r="AC17" s="29" t="n"/>
+      <c r="Y17" s="15" t="n"/>
+      <c r="Z17" s="16" t="n"/>
+      <c r="AA17" s="17" t="n"/>
+      <c r="AB17" s="18" t="n"/>
+      <c r="AC17" s="19" t="n"/>
       <c r="AD17" s="29" t="n"/>
-      <c r="AE17" s="29" t="n"/>
-      <c r="AF17" s="29" t="n"/>
-      <c r="AG17" s="29" t="n"/>
-      <c r="AH17" s="29" t="n"/>
-      <c r="AI17" s="29" t="n"/>
-      <c r="AJ17" s="29" t="n"/>
-      <c r="AK17" s="29" t="n"/>
-      <c r="AL17" s="29" t="n"/>
-      <c r="AM17" s="29" t="n"/>
-      <c r="AN17" s="29" t="n"/>
-      <c r="AO17" s="29" t="n"/>
-      <c r="AP17" s="29" t="n"/>
-      <c r="AQ17" s="29" t="n"/>
-      <c r="AR17" s="29" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>person</t>
         </is>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
-          <t>Parent ID</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>मूल ID</t>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Asli ID</t>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>ID ya mzazi</t>
-        </is>
-      </c>
-      <c r="G18" s="29" t="n"/>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>identifiant du parent</t>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="J18" s="29" t="n"/>
@@ -1831,11 +1799,7 @@
       <c r="AB18" s="29" t="n"/>
       <c r="AC18" s="29" t="n"/>
       <c r="AD18" s="29" t="n"/>
-      <c r="AE18" s="29" t="inlineStr">
-        <is>
-          <t>PARENT</t>
-        </is>
-      </c>
+      <c r="AE18" s="29" t="n"/>
       <c r="AF18" s="29" t="n"/>
       <c r="AG18" s="29" t="n"/>
       <c r="AH18" s="29" t="n"/>
@@ -1858,34 +1822,34 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
-          <t>Person Type</t>
+          <t>Parent ID</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>व्यक्ति के प्रकार</t>
+          <t>मूल ID</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>Tipe Orang</t>
+          <t>Asli ID</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>Jina</t>
+          <t>ID ya mzazi</t>
         </is>
       </c>
       <c r="G19" s="29" t="n"/>
       <c r="H19" s="29" t="n"/>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>identifiant du parent</t>
         </is>
       </c>
       <c r="J19" s="29" t="n"/>
@@ -1911,7 +1875,7 @@
       <c r="AD19" s="29" t="n"/>
       <c r="AE19" s="29" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>PARENT</t>
         </is>
       </c>
       <c r="AF19" s="29" t="n"/>
@@ -1931,50 +1895,42 @@
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Person Type</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>नाम</t>
+          <t>व्यक्ति के प्रकार</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Tipe Orang</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Majina</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>नाम</t>
-        </is>
-      </c>
+          <t>Jina</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="n"/>
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="J20" s="29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="J20" s="29" t="n"/>
       <c r="K20" s="29" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -1995,7 +1951,11 @@
       <c r="AB20" s="29" t="n"/>
       <c r="AC20" s="29" t="n"/>
       <c r="AD20" s="29" t="n"/>
-      <c r="AE20" s="29" t="n"/>
+      <c r="AE20" s="29" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="AF20" s="29" t="n"/>
       <c r="AG20" s="29" t="n"/>
       <c r="AH20" s="29" t="n"/>
@@ -2011,97 +1971,64 @@
       <c r="AR20" s="29" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>short_name</t>
-        </is>
-      </c>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>Short name</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="29" t="n"/>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="29" t="n"/>
-      <c r="N21" s="29" t="inlineStr">
-        <is>
-          <t>string-length(.) &lt;= 10</t>
-        </is>
-      </c>
-      <c r="O21" s="29" t="inlineStr">
-        <is>
-          <t>Short name can not be more than 10 characters long.</t>
-        </is>
-      </c>
-      <c r="P21" s="29" t="n"/>
-      <c r="Q21" s="29" t="n"/>
-      <c r="R21" s="29" t="n"/>
-      <c r="S21" s="29" t="n"/>
-      <c r="T21" s="29" t="n"/>
-      <c r="U21" s="29" t="n"/>
-      <c r="V21" s="29" t="n"/>
-      <c r="W21" s="29" t="n"/>
-      <c r="X21" s="24" t="inlineStr">
-        <is>
-          <t>Please enter a short name that is preferred by the person.</t>
-        </is>
-      </c>
-      <c r="Y21" s="29" t="n"/>
-      <c r="Z21" s="29" t="n"/>
-      <c r="AA21" s="29" t="n"/>
-      <c r="AB21" s="29" t="n"/>
-      <c r="AC21" s="29" t="n"/>
-      <c r="AD21" s="29" t="n"/>
-      <c r="AE21" s="29" t="n"/>
-      <c r="AF21" s="29" t="n"/>
-      <c r="AG21" s="29" t="n"/>
-      <c r="AH21" s="29" t="n"/>
-      <c r="AI21" s="29" t="n"/>
-      <c r="AJ21" s="29" t="n"/>
-      <c r="AK21" s="29" t="n"/>
-      <c r="AL21" s="29" t="n"/>
-      <c r="AM21" s="29" t="n"/>
-      <c r="AN21" s="29" t="n"/>
-      <c r="AO21" s="29" t="n"/>
-      <c r="AP21" s="29" t="n"/>
-      <c r="AQ21" s="29" t="n"/>
-      <c r="AR21" s="29" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>created_by_role</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>/data/inputs/user/roles</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>नाम</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="inlineStr">
+        <is>
+          <t>Majina</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>नाम</t>
+        </is>
+      </c>
       <c r="H22" s="29" t="n"/>
-      <c r="I22" s="25" t="n"/>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
       <c r="J22" s="29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2118,11 +2045,7 @@
       <c r="S22" s="29" t="n"/>
       <c r="T22" s="29" t="n"/>
       <c r="U22" s="29" t="n"/>
-      <c r="V22" s="29" t="inlineStr">
-        <is>
-          <t>../ephemeral_dob/dob_iso</t>
-        </is>
-      </c>
+      <c r="V22" s="29" t="n"/>
       <c r="W22" s="29" t="n"/>
       <c r="X22" s="29" t="n"/>
       <c r="Y22" s="29" t="n"/>
@@ -2149,40 +2072,56 @@
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>date_of_birth_method</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="n"/>
+          <t>short_name</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Short name</t>
+        </is>
+      </c>
       <c r="D23" s="29" t="n"/>
       <c r="E23" s="29" t="n"/>
       <c r="F23" s="29" t="n"/>
       <c r="G23" s="29" t="n"/>
       <c r="H23" s="29" t="n"/>
       <c r="I23" s="29" t="n"/>
-      <c r="J23" s="29" t="n"/>
+      <c r="J23" s="29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="K23" s="29" t="n"/>
       <c r="L23" s="29" t="n"/>
       <c r="M23" s="29" t="n"/>
-      <c r="N23" s="29" t="n"/>
-      <c r="O23" s="29" t="n"/>
+      <c r="N23" s="29" t="inlineStr">
+        <is>
+          <t>string-length(.) &lt;= 10</t>
+        </is>
+      </c>
+      <c r="O23" s="29" t="inlineStr">
+        <is>
+          <t>Short name can not be more than 10 characters long.</t>
+        </is>
+      </c>
       <c r="P23" s="29" t="n"/>
       <c r="Q23" s="29" t="n"/>
       <c r="R23" s="29" t="n"/>
       <c r="S23" s="29" t="n"/>
       <c r="T23" s="29" t="n"/>
       <c r="U23" s="29" t="n"/>
-      <c r="V23" s="29" t="inlineStr">
-        <is>
-          <t>../ephemeral_dob/dob_method</t>
-        </is>
-      </c>
+      <c r="V23" s="29" t="n"/>
       <c r="W23" s="29" t="n"/>
-      <c r="X23" s="29" t="n"/>
+      <c r="X23" s="24" t="inlineStr">
+        <is>
+          <t>Please enter a short name that is preferred by the person.</t>
+        </is>
+      </c>
       <c r="Y23" s="29" t="n"/>
       <c r="Z23" s="29" t="n"/>
       <c r="AA23" s="29" t="n"/>
@@ -2207,26 +2146,26 @@
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>ephemeral_dob</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="29" t="n"/>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
       <c r="H24" s="29" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K24" s="29" t="n"/>
       <c r="L24" s="29" t="n"/>
       <c r="M24" s="29" t="n"/>
@@ -2238,7 +2177,11 @@
       <c r="S24" s="29" t="n"/>
       <c r="T24" s="29" t="n"/>
       <c r="U24" s="29" t="n"/>
-      <c r="V24" s="29" t="n"/>
+      <c r="V24" s="29" t="inlineStr">
+        <is>
+          <t>../ephemeral_dob/dob_iso</t>
+        </is>
+      </c>
       <c r="W24" s="29" t="n"/>
       <c r="X24" s="29" t="n"/>
       <c r="Y24" s="29" t="n"/>
@@ -2265,60 +2208,40 @@
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>dob_calendar</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
+          <t>date_of_birth_method</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n"/>
       <c r="D25" s="29" t="n"/>
       <c r="E25" s="29" t="n"/>
       <c r="F25" s="29" t="n"/>
       <c r="G25" s="29" t="n"/>
       <c r="H25" s="29" t="n"/>
       <c r="I25" s="29" t="n"/>
-      <c r="J25" s="29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K25" s="29" t="inlineStr">
-        <is>
-          <t>not(selected(../dob_method,'approx'))</t>
-        </is>
-      </c>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
       <c r="L25" s="29" t="n"/>
       <c r="M25" s="29" t="n"/>
-      <c r="N25" s="29" t="inlineStr">
-        <is>
-          <t>. &lt;= now()</t>
-        </is>
-      </c>
-      <c r="O25" s="29" t="inlineStr">
-        <is>
-          <t>Date must be before today</t>
-        </is>
-      </c>
+      <c r="N25" s="29" t="n"/>
+      <c r="O25" s="29" t="n"/>
       <c r="P25" s="29" t="n"/>
       <c r="Q25" s="29" t="n"/>
       <c r="R25" s="29" t="n"/>
       <c r="S25" s="29" t="n"/>
       <c r="T25" s="29" t="n"/>
       <c r="U25" s="29" t="n"/>
-      <c r="V25" s="29" t="n"/>
+      <c r="V25" s="29" t="inlineStr">
+        <is>
+          <t>../ephemeral_dob/dob_method</t>
+        </is>
+      </c>
       <c r="W25" s="29" t="n"/>
-      <c r="X25" s="29" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
+      <c r="X25" s="29" t="n"/>
       <c r="Y25" s="29" t="n"/>
       <c r="Z25" s="29" t="n"/>
       <c r="AA25" s="29" t="n"/>
@@ -2343,17 +2266,17 @@
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>age_label</t>
+          <t>ephemeral_dob</t>
         </is>
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>**Please enter date of birth**</t>
+          <t>NO_LABEL</t>
         </is>
       </c>
       <c r="D26" s="29" t="n"/>
@@ -2363,11 +2286,7 @@
       <c r="H26" s="29" t="n"/>
       <c r="I26" s="29" t="n"/>
       <c r="J26" s="29" t="n"/>
-      <c r="K26" s="29" t="inlineStr">
-        <is>
-          <t>selected(../dob_method,'approx')</t>
-        </is>
-      </c>
+      <c r="K26" s="29" t="n"/>
       <c r="L26" s="29" t="n"/>
       <c r="M26" s="29" t="n"/>
       <c r="N26" s="29" t="n"/>
@@ -2405,17 +2324,17 @@
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>age_years</t>
+          <t>dob_calendar</t>
         </is>
       </c>
       <c r="C27" s="29" t="inlineStr">
         <is>
-          <t>Years</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D27" s="29" t="n"/>
@@ -2431,19 +2350,19 @@
       </c>
       <c r="K27" s="29" t="inlineStr">
         <is>
-          <t>selected(../dob_method,'approx')</t>
+          <t>not(selected(../dob_method,'approx'))</t>
         </is>
       </c>
       <c r="L27" s="29" t="n"/>
       <c r="M27" s="29" t="n"/>
       <c r="N27" s="29" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 130</t>
+          <t>. &lt;= now()</t>
         </is>
       </c>
       <c r="O27" s="29" t="inlineStr">
         <is>
-          <t>Age must be between 0 and 130</t>
+          <t>Date must be before today</t>
         </is>
       </c>
       <c r="P27" s="29" t="n"/>
@@ -2454,7 +2373,11 @@
       <c r="U27" s="29" t="n"/>
       <c r="V27" s="29" t="n"/>
       <c r="W27" s="29" t="n"/>
-      <c r="X27" s="29" t="n"/>
+      <c r="X27" s="29" t="inlineStr">
+        <is>
+          <t>Date of Birth</t>
+        </is>
+      </c>
       <c r="Y27" s="29" t="n"/>
       <c r="Z27" s="29" t="n"/>
       <c r="AA27" s="29" t="n"/>
@@ -2479,17 +2402,17 @@
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>age_months</t>
+          <t>age_label</t>
         </is>
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>Months</t>
+          <t>**Please enter date of birth**</t>
         </is>
       </c>
       <c r="D28" s="29" t="n"/>
@@ -2506,16 +2429,8 @@
       </c>
       <c r="L28" s="29" t="n"/>
       <c r="M28" s="29" t="n"/>
-      <c r="N28" s="29" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 11</t>
-        </is>
-      </c>
-      <c r="O28" s="29" t="inlineStr">
-        <is>
-          <t>Months must between 0 and 11</t>
-        </is>
-      </c>
+      <c r="N28" s="29" t="n"/>
+      <c r="O28" s="29" t="n"/>
       <c r="P28" s="29" t="n"/>
       <c r="Q28" s="29" t="n"/>
       <c r="R28" s="29" t="n"/>
@@ -2549,17 +2464,17 @@
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>select_multiple select_dob_method</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>dob_method</t>
+          <t>age_years</t>
         </is>
       </c>
       <c r="C29" s="29" t="inlineStr">
         <is>
-          <t>DELETE_THIS_LINE</t>
+          <t>Years</t>
         </is>
       </c>
       <c r="D29" s="29" t="n"/>
@@ -2568,16 +2483,28 @@
       <c r="G29" s="29" t="n"/>
       <c r="H29" s="29" t="n"/>
       <c r="I29" s="29" t="n"/>
-      <c r="J29" s="29" t="n"/>
-      <c r="K29" s="29" t="n"/>
-      <c r="L29" s="29" t="inlineStr">
-        <is>
-          <t>columns</t>
-        </is>
-      </c>
+      <c r="J29" s="29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K29" s="29" t="inlineStr">
+        <is>
+          <t>selected(../dob_method,'approx')</t>
+        </is>
+      </c>
+      <c r="L29" s="29" t="n"/>
       <c r="M29" s="29" t="n"/>
-      <c r="N29" s="29" t="n"/>
-      <c r="O29" s="29" t="n"/>
+      <c r="N29" s="29" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 130</t>
+        </is>
+      </c>
+      <c r="O29" s="29" t="inlineStr">
+        <is>
+          <t>Age must be between 0 and 130</t>
+        </is>
+      </c>
       <c r="P29" s="29" t="n"/>
       <c r="Q29" s="29" t="n"/>
       <c r="R29" s="29" t="n"/>
@@ -2611,15 +2538,19 @@
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>dob_approx</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="n"/>
+          <t>age_months</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
       <c r="D30" s="29" t="n"/>
       <c r="E30" s="29" t="n"/>
       <c r="F30" s="29" t="n"/>
@@ -2627,22 +2558,30 @@
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="29" t="n"/>
       <c r="J30" s="29" t="n"/>
-      <c r="K30" s="29" t="n"/>
+      <c r="K30" s="29" t="inlineStr">
+        <is>
+          <t>selected(../dob_method,'approx')</t>
+        </is>
+      </c>
       <c r="L30" s="29" t="n"/>
       <c r="M30" s="29" t="n"/>
-      <c r="N30" s="29" t="n"/>
-      <c r="O30" s="29" t="n"/>
+      <c r="N30" s="29" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 11</t>
+        </is>
+      </c>
+      <c r="O30" s="29" t="inlineStr">
+        <is>
+          <t>Months must between 0 and 11</t>
+        </is>
+      </c>
       <c r="P30" s="29" t="n"/>
       <c r="Q30" s="29" t="n"/>
       <c r="R30" s="29" t="n"/>
       <c r="S30" s="29" t="n"/>
       <c r="T30" s="29" t="n"/>
       <c r="U30" s="29" t="n"/>
-      <c r="V30" s="25" t="inlineStr">
-        <is>
-          <t>add-date(today(), 0-${age_years}, 0-${age_months})</t>
-        </is>
-      </c>
+      <c r="V30" s="29" t="n"/>
       <c r="W30" s="29" t="n"/>
       <c r="X30" s="29" t="n"/>
       <c r="Y30" s="29" t="n"/>
@@ -2669,15 +2608,19 @@
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_multiple select_dob_method</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>dob_raw</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="n"/>
+          <t>dob_method</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>DELETE_THIS_LINE</t>
+        </is>
+      </c>
       <c r="D31" s="29" t="n"/>
       <c r="E31" s="29" t="n"/>
       <c r="F31" s="29" t="n"/>
@@ -2686,7 +2629,11 @@
       <c r="I31" s="29" t="n"/>
       <c r="J31" s="29" t="n"/>
       <c r="K31" s="29" t="n"/>
-      <c r="L31" s="29" t="n"/>
+      <c r="L31" s="29" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
       <c r="M31" s="29" t="n"/>
       <c r="N31" s="29" t="n"/>
       <c r="O31" s="29" t="n"/>
@@ -2694,15 +2641,9 @@
       <c r="Q31" s="29" t="n"/>
       <c r="R31" s="29" t="n"/>
       <c r="S31" s="29" t="n"/>
-      <c r="T31" s="25" t="n"/>
+      <c r="T31" s="29" t="n"/>
       <c r="U31" s="29" t="n"/>
-      <c r="V31" s="26" t="inlineStr">
-        <is>
-          <t>if(not(selected( ${dob_method},'approx')), 
-${dob_calendar},
-${dob_approx})</t>
-        </is>
-      </c>
+      <c r="V31" s="29" t="n"/>
       <c r="W31" s="29" t="n"/>
       <c r="X31" s="29" t="n"/>
       <c r="Y31" s="29" t="n"/>
@@ -2734,7 +2675,7 @@
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>dob_iso</t>
+          <t>dob_approx</t>
         </is>
       </c>
       <c r="C32" s="25" t="n"/>
@@ -2756,9 +2697,9 @@
       <c r="S32" s="29" t="n"/>
       <c r="T32" s="29" t="n"/>
       <c r="U32" s="29" t="n"/>
-      <c r="V32" s="29" t="inlineStr">
-        <is>
-          <t>format-date-time(../dob_raw,"%Y-%m-%d")</t>
+      <c r="V32" s="25" t="inlineStr">
+        <is>
+          <t>add-date(today(), 0-${age_years}, 0-${age_months})</t>
         </is>
       </c>
       <c r="W32" s="29" t="n"/>
@@ -2787,21 +2728,15 @@
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>dob_debug</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>DOB Approx: ${dob_approx}
-DOB Calendar: ${dob_calendar}
-DOB ISO: ${dob_iso}</t>
-        </is>
-      </c>
+          <t>dob_raw</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n"/>
       <c r="D33" s="29" t="n"/>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
@@ -2809,11 +2744,7 @@
       <c r="H33" s="29" t="n"/>
       <c r="I33" s="29" t="n"/>
       <c r="J33" s="29" t="n"/>
-      <c r="K33" s="29" t="inlineStr">
-        <is>
-          <t>false()</t>
-        </is>
-      </c>
+      <c r="K33" s="29" t="n"/>
       <c r="L33" s="29" t="n"/>
       <c r="M33" s="29" t="n"/>
       <c r="N33" s="29" t="n"/>
@@ -2822,9 +2753,15 @@
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="29" t="n"/>
       <c r="S33" s="29" t="n"/>
-      <c r="T33" s="29" t="n"/>
+      <c r="T33" s="25" t="n"/>
       <c r="U33" s="29" t="n"/>
-      <c r="V33" s="29" t="n"/>
+      <c r="V33" s="26" t="inlineStr">
+        <is>
+          <t>if(not(selected( ${dob_method},'approx')), 
+${dob_calendar},
+${dob_approx})</t>
+        </is>
+      </c>
       <c r="W33" s="29" t="n"/>
       <c r="X33" s="29" t="n"/>
       <c r="Y33" s="29" t="n"/>
@@ -2851,11 +2788,15 @@
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="29" t="n"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>dob_iso</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n"/>
       <c r="D34" s="29" t="n"/>
       <c r="E34" s="29" t="n"/>
       <c r="F34" s="29" t="n"/>
@@ -2874,7 +2815,11 @@
       <c r="S34" s="29" t="n"/>
       <c r="T34" s="29" t="n"/>
       <c r="U34" s="29" t="n"/>
-      <c r="V34" s="29" t="n"/>
+      <c r="V34" s="29" t="inlineStr">
+        <is>
+          <t>format-date-time(../dob_raw,"%Y-%m-%d")</t>
+        </is>
+      </c>
       <c r="W34" s="29" t="n"/>
       <c r="X34" s="29" t="n"/>
       <c r="Y34" s="29" t="n"/>
@@ -2901,56 +2846,34 @@
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>select_one male_female</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>लिंग</t>
-        </is>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
-        <is>
-          <t>Jenis kelamin</t>
-        </is>
-      </c>
-      <c r="F35" s="29" t="inlineStr">
-        <is>
-          <t>Jinsia</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>लिंग</t>
-        </is>
-      </c>
+          <t>dob_debug</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>DOB Approx: ${dob_approx}
+DOB Calendar: ${dob_calendar}
+DOB ISO: ${dob_iso}</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="29" t="n"/>
       <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="inlineStr">
-        <is>
-          <t>Sexe</t>
-        </is>
-      </c>
-      <c r="J35" s="29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="29" t="inlineStr">
-        <is>
-          <t>columns</t>
-        </is>
-      </c>
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="inlineStr">
+        <is>
+          <t>false()</t>
+        </is>
+      </c>
+      <c r="L35" s="29" t="n"/>
       <c r="M35" s="29" t="n"/>
       <c r="N35" s="29" t="n"/>
       <c r="O35" s="29" t="n"/>
@@ -2987,73 +2910,29 @@
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>tel</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>फोन नंबर</t>
-        </is>
-      </c>
-      <c r="E36" s="29" t="inlineStr">
-        <is>
-          <t>Nomor Telepon</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr">
-        <is>
-          <t>Nambari ya simu</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>फोन नम्बर</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
       <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="inlineStr">
-        <is>
-          <t>Téléphone</t>
-        </is>
-      </c>
+      <c r="I36" s="29" t="n"/>
       <c r="J36" s="29" t="n"/>
       <c r="K36" s="29" t="n"/>
       <c r="L36" s="29" t="n"/>
       <c r="M36" s="29" t="n"/>
-      <c r="N36" s="29" t="inlineStr">
-        <is>
-          <t>true()</t>
-        </is>
-      </c>
-      <c r="O36" s="29" t="inlineStr">
-        <is>
-          <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
-        </is>
-      </c>
-      <c r="P36" s="28" t="inlineStr">
-        <is>
-          <t>कृपया एक सही स्थानीय नंबर दर्ज करें, या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें, जिसमें एक प्लस साइन (+) और देश कोड शामिल है। उदाहरण के लिए: +914712345678</t>
-        </is>
-      </c>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="29" t="n"/>
+      <c r="P36" s="29" t="n"/>
       <c r="Q36" s="29" t="n"/>
       <c r="R36" s="29" t="n"/>
       <c r="S36" s="29" t="n"/>
       <c r="T36" s="29" t="n"/>
-      <c r="U36" s="29" t="inlineStr">
-        <is>
-          <t>Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
-        </is>
-      </c>
+      <c r="U36" s="29" t="n"/>
       <c r="V36" s="29" t="n"/>
       <c r="W36" s="29" t="n"/>
       <c r="X36" s="29" t="n"/>
@@ -3081,73 +2960,65 @@
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>select_one male_female</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>phone_alternate</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="C37" s="29" t="inlineStr">
         <is>
-          <t>Alternate Phone Number</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>अन्य फोन नंबर</t>
+          <t>लिंग</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Nomor Telepon Alternatif</t>
+          <t>Jenis kelamin</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>nambari nyingine ya simu</t>
+          <t>Jinsia</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
         <is>
-          <t>अन्य फोन नम्बर</t>
+          <t>लिंग</t>
         </is>
       </c>
       <c r="H37" s="29" t="n"/>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>Téléphone alternatif</t>
-        </is>
-      </c>
-      <c r="J37" s="29" t="n"/>
+          <t>Sexe</t>
+        </is>
+      </c>
+      <c r="J37" s="29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K37" s="29" t="n"/>
-      <c r="L37" s="29" t="n"/>
+      <c r="L37" s="29" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
       <c r="M37" s="29" t="n"/>
-      <c r="N37" s="29" t="inlineStr">
-        <is>
-          <t>true()</t>
-        </is>
-      </c>
-      <c r="O37" s="29" t="inlineStr">
-        <is>
-          <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
-        </is>
-      </c>
-      <c r="P37" s="28" t="inlineStr">
-        <is>
-          <t>कृपया एक सही स्थानीय नंबर दर्ज करें, या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें, जिसमें एक प्लस साइन (+) और देश कोड शामिल है। उदाहरण के लिए: +914712345678</t>
-        </is>
-      </c>
+      <c r="N37" s="29" t="n"/>
+      <c r="O37" s="29" t="n"/>
+      <c r="P37" s="29" t="n"/>
       <c r="Q37" s="29" t="n"/>
       <c r="R37" s="29" t="n"/>
       <c r="S37" s="29" t="n"/>
       <c r="T37" s="29" t="n"/>
-      <c r="U37" s="29" t="inlineStr">
-        <is>
-          <t>Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
-        </is>
-      </c>
+      <c r="U37" s="29" t="n"/>
       <c r="V37" s="29" t="n"/>
       <c r="W37" s="29" t="n"/>
       <c r="X37" s="29" t="n"/>
@@ -3175,90 +3046,82 @@
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>select_one roles</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>भूमिका</t>
+          <t>फोन नंबर</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Peran</t>
+          <t>Nomor Telepon</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Jukumu</t>
+          <t>Nambari ya simu</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>भूमिका</t>
+          <t>फोन नम्बर</t>
         </is>
       </c>
       <c r="H38" s="29" t="n"/>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>Rôle</t>
+          <t>Téléphone</t>
         </is>
       </c>
       <c r="J38" s="29" t="n"/>
       <c r="K38" s="29" t="n"/>
       <c r="L38" s="29" t="n"/>
       <c r="M38" s="29" t="n"/>
-      <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
-      <c r="P38" s="29" t="n"/>
+      <c r="N38" s="29" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="O38" s="29" t="inlineStr">
+        <is>
+          <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
+        </is>
+      </c>
+      <c r="P38" s="28" t="inlineStr">
+        <is>
+          <t>कृपया एक सही स्थानीय नंबर दर्ज करें, या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें, जिसमें एक प्लस साइन (+) और देश कोड शामिल है। उदाहरण के लिए: +914712345678</t>
+        </is>
+      </c>
       <c r="Q38" s="29" t="n"/>
       <c r="R38" s="29" t="n"/>
       <c r="S38" s="29" t="n"/>
       <c r="T38" s="29" t="n"/>
-      <c r="U38" s="29" t="n"/>
+      <c r="U38" s="29" t="inlineStr">
+        <is>
+          <t>Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
+        </is>
+      </c>
       <c r="V38" s="29" t="n"/>
       <c r="W38" s="29" t="n"/>
-      <c r="X38" s="29" t="inlineStr">
-        <is>
-          <t>Select the role that best suits this person</t>
-        </is>
-      </c>
-      <c r="Y38" s="23" t="inlineStr">
-        <is>
-          <t>उस भूमिका का चयन करें जो इस व्यक्ति को सबसे अच्छा सूट करता है</t>
-        </is>
-      </c>
-      <c r="Z38" s="29" t="inlineStr">
-        <is>
-          <t>Pilih peran yang paling cocok untuk orang ini</t>
-        </is>
-      </c>
-      <c r="AA38" s="29" t="inlineStr">
-        <is>
-          <t>Chagua jukumu linachoambatana na huyu mtu</t>
-        </is>
-      </c>
-      <c r="AB38" s="23" t="inlineStr">
-        <is>
-          <t>यस व्यक्तिका लागि उपयुक्त भूमिका छान्नुहोस्</t>
-        </is>
-      </c>
+      <c r="X38" s="29" t="n"/>
+      <c r="Y38" s="29" t="n"/>
+      <c r="Z38" s="29" t="n"/>
+      <c r="AA38" s="29" t="n"/>
+      <c r="AB38" s="29" t="n"/>
       <c r="AC38" s="29" t="n"/>
-      <c r="AD38" s="29" t="inlineStr">
-        <is>
-          <t>Sélectionnez le rôle qui convient le mieux à cette personne</t>
-        </is>
-      </c>
+      <c r="AD38" s="29" t="n"/>
       <c r="AE38" s="29" t="n"/>
       <c r="AF38" s="29" t="n"/>
       <c r="AG38" s="29" t="n"/>
@@ -3277,65 +3140,73 @@
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>role_other</t>
+          <t>phone_alternate</t>
         </is>
       </c>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>Specify other</t>
+          <t>Alternate Phone Number</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>अन्य का उल्‍लेख करें</t>
+          <t>अन्य फोन नंबर</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Tentukan lainnya</t>
+          <t>Nomor Telepon Alternatif</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jukumu lingine lelote</t>
+          <t>nambari nyingine ya simu</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>अन्य उल्लेख गर्नुहोस्</t>
+          <t>अन्य फोन नम्बर</t>
         </is>
       </c>
       <c r="H39" s="29" t="n"/>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>Autre rôle</t>
-        </is>
-      </c>
-      <c r="J39" s="29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K39" s="29" t="inlineStr">
-        <is>
-          <t>selected( ${role},'other')</t>
-        </is>
-      </c>
+          <t>Téléphone alternatif</t>
+        </is>
+      </c>
+      <c r="J39" s="29" t="n"/>
+      <c r="K39" s="29" t="n"/>
       <c r="L39" s="29" t="n"/>
       <c r="M39" s="29" t="n"/>
-      <c r="N39" s="29" t="n"/>
-      <c r="O39" s="29" t="n"/>
-      <c r="P39" s="29" t="n"/>
+      <c r="N39" s="29" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="O39" s="29" t="inlineStr">
+        <is>
+          <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
+        </is>
+      </c>
+      <c r="P39" s="28" t="inlineStr">
+        <is>
+          <t>कृपया एक सही स्थानीय नंबर दर्ज करें, या मानक अंतरराष्ट्रीय प्रारूप का उपयोग करें, जिसमें एक प्लस साइन (+) और देश कोड शामिल है। उदाहरण के लिए: +914712345678</t>
+        </is>
+      </c>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="29" t="n"/>
       <c r="S39" s="29" t="n"/>
       <c r="T39" s="29" t="n"/>
-      <c r="U39" s="29" t="n"/>
+      <c r="U39" s="29" t="inlineStr">
+        <is>
+          <t>Veuillez entrer un numéro local valide ou utiliser le format international standard, qui comprend un signe plus (+) et le code du pays. Par exemple: +254712345678</t>
+        </is>
+      </c>
       <c r="V39" s="29" t="n"/>
       <c r="W39" s="29" t="n"/>
       <c r="X39" s="29" t="n"/>
@@ -3361,132 +3232,97 @@
       <c r="AR39" s="29" t="n"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>external_id</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>External ID</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>बाहरी ID</t>
-        </is>
-      </c>
-      <c r="E40" s="29" t="inlineStr">
-        <is>
-          <t>Eksternal ID</t>
-        </is>
-      </c>
-      <c r="F40" s="29" t="inlineStr">
-        <is>
-          <t>ID ya nje</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>बाहिरी ID</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n"/>
-      <c r="I40" s="29" t="inlineStr">
-        <is>
-          <t>Identifiant externe</t>
-        </is>
-      </c>
-      <c r="J40" s="29" t="n"/>
-      <c r="K40" s="29" t="n"/>
-      <c r="L40" s="29" t="n"/>
-      <c r="M40" s="29" t="n"/>
-      <c r="N40" s="29" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
-      <c r="Q40" s="29" t="n"/>
-      <c r="R40" s="29" t="n"/>
-      <c r="S40" s="29" t="n"/>
-      <c r="T40" s="29" t="n"/>
-      <c r="U40" s="29" t="n"/>
-      <c r="V40" s="29" t="n"/>
-      <c r="W40" s="29" t="n"/>
-      <c r="X40" s="29" t="n"/>
-      <c r="Y40" s="29" t="n"/>
-      <c r="Z40" s="29" t="n"/>
-      <c r="AA40" s="29" t="n"/>
-      <c r="AB40" s="29" t="n"/>
-      <c r="AC40" s="29" t="n"/>
-      <c r="AD40" s="29" t="n"/>
-      <c r="AE40" s="29" t="n"/>
-      <c r="AF40" s="29" t="n"/>
-      <c r="AG40" s="29" t="n"/>
-      <c r="AH40" s="29" t="n"/>
-      <c r="AI40" s="29" t="n"/>
-      <c r="AJ40" s="29" t="n"/>
-      <c r="AK40" s="29" t="n"/>
-      <c r="AL40" s="29" t="n"/>
-      <c r="AM40" s="29" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="29" t="n"/>
-      <c r="AP40" s="29" t="n"/>
-      <c r="AQ40" s="29" t="n"/>
-      <c r="AR40" s="29" t="n"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>display_user_role</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Logged in as: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>लॉग इन भूमिका: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Masuk sebagai: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Umeingia kama: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>लग इन भूमिका: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Connecté en tant que: ${created_by_role}</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>false()</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>select_one roles</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C41" s="29" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>नोट्स</t>
+          <t>भूमिका</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Catatan</t>
+          <t>Peran</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Maelezo</t>
+          <t>Jukumu</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>टिप्पणी</t>
+          <t>भूमिका</t>
         </is>
       </c>
       <c r="H41" s="29" t="n"/>
       <c r="I41" s="29" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Rôle</t>
         </is>
       </c>
       <c r="J41" s="29" t="n"/>
       <c r="K41" s="29" t="n"/>
-      <c r="L41" s="29" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="L41" s="29" t="n"/>
       <c r="M41" s="29" t="n"/>
       <c r="N41" s="29" t="n"/>
       <c r="O41" s="29" t="n"/>
@@ -3497,14 +3333,42 @@
       <c r="T41" s="29" t="n"/>
       <c r="U41" s="29" t="n"/>
       <c r="V41" s="29" t="n"/>
-      <c r="W41" s="29" t="n"/>
-      <c r="X41" s="29" t="n"/>
-      <c r="Y41" s="29" t="n"/>
-      <c r="Z41" s="29" t="n"/>
-      <c r="AA41" s="29" t="n"/>
-      <c r="AB41" s="29" t="n"/>
+      <c r="W41" s="29" t="inlineStr">
+        <is>
+          <t>selected(creator_role, ${created_by_role})</t>
+        </is>
+      </c>
+      <c r="X41" s="29" t="inlineStr">
+        <is>
+          <t>Select the role that best suits this person</t>
+        </is>
+      </c>
+      <c r="Y41" s="23" t="inlineStr">
+        <is>
+          <t>उस भूमिका का चयन करें जो इस व्यक्ति को सबसे अच्छा सूट करता है</t>
+        </is>
+      </c>
+      <c r="Z41" s="29" t="inlineStr">
+        <is>
+          <t>Pilih peran yang paling cocok untuk orang ini</t>
+        </is>
+      </c>
+      <c r="AA41" s="29" t="inlineStr">
+        <is>
+          <t>Chagua jukumu linachoambatana na huyu mtu</t>
+        </is>
+      </c>
+      <c r="AB41" s="23" t="inlineStr">
+        <is>
+          <t>यस व्यक्तिका लागि उपयुक्त भूमिका छान्नुहोस्</t>
+        </is>
+      </c>
       <c r="AC41" s="29" t="n"/>
-      <c r="AD41" s="29" t="n"/>
+      <c r="AD41" s="29" t="inlineStr">
+        <is>
+          <t>Sélectionnez le rôle qui convient le mieux à cette personne</t>
+        </is>
+      </c>
       <c r="AE41" s="29" t="n"/>
       <c r="AF41" s="29" t="n"/>
       <c r="AG41" s="29" t="n"/>
@@ -3523,47 +3387,55 @@
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>user_for_contact</t>
+          <t>role_other</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D42" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
+          <t>Specify other</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>अन्य का उल्‍लेख करें</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
+          <t>Tentukan lainnya</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="G42" s="29" t="inlineStr">
-        <is>
-          <t>NO_LABEL</t>
+          <t xml:space="preserve"> Jukumu lingine lelote</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>अन्य उल्लेख गर्नुहोस्</t>
         </is>
       </c>
       <c r="H42" s="29" t="n"/>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="J42" s="29" t="n"/>
-      <c r="K42" s="29" t="n"/>
+          <t>Autre rôle</t>
+        </is>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>selected( ${role},'other')</t>
+        </is>
+      </c>
       <c r="L42" s="29" t="n"/>
       <c r="M42" s="29" t="n"/>
       <c r="N42" s="29" t="n"/>
@@ -3601,21 +3473,45 @@
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="29" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="29" t="n"/>
-      <c r="G43" s="29" t="n"/>
+          <t>external_id</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>External ID</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>बाहरी ID</t>
+        </is>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>Eksternal ID</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>ID ya nje</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>बाहिरी ID</t>
+        </is>
+      </c>
       <c r="H43" s="29" t="n"/>
-      <c r="I43" s="29" t="n"/>
+      <c r="I43" s="29" t="inlineStr">
+        <is>
+          <t>Identifiant externe</t>
+        </is>
+      </c>
       <c r="J43" s="29" t="n"/>
       <c r="K43" s="29" t="n"/>
       <c r="L43" s="29" t="n"/>
@@ -3628,11 +3524,7 @@
       <c r="S43" s="29" t="n"/>
       <c r="T43" s="29" t="n"/>
       <c r="U43" s="29" t="n"/>
-      <c r="V43" s="29" t="inlineStr">
-        <is>
-          <t>false()</t>
-        </is>
-      </c>
+      <c r="V43" s="29" t="n"/>
       <c r="W43" s="29" t="n"/>
       <c r="X43" s="29" t="n"/>
       <c r="Y43" s="29" t="n"/>
@@ -3659,20 +3551,52 @@
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="29" t="n"/>
-      <c r="G44" s="29" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>नोट्स</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>Maelezo</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>टिप्पणी</t>
+        </is>
+      </c>
       <c r="H44" s="29" t="n"/>
-      <c r="I44" s="29" t="n"/>
+      <c r="I44" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
       <c r="J44" s="29" t="n"/>
       <c r="K44" s="29" t="n"/>
-      <c r="L44" s="29" t="n"/>
+      <c r="L44" s="29" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="M44" s="29" t="n"/>
       <c r="N44" s="29" t="n"/>
       <c r="O44" s="29" t="n"/>
@@ -3714,7 +3638,7 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>user_for_contact</t>
         </is>
       </c>
       <c r="C45" s="29" t="inlineStr">
@@ -3750,11 +3674,7 @@
       </c>
       <c r="J45" s="29" t="n"/>
       <c r="K45" s="29" t="n"/>
-      <c r="L45" s="29" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
+      <c r="L45" s="29" t="n"/>
       <c r="M45" s="29" t="n"/>
       <c r="N45" s="29" t="n"/>
       <c r="O45" s="29" t="n"/>
@@ -3796,7 +3716,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>create</t>
         </is>
       </c>
       <c r="C46" s="29" t="n"/>
@@ -3820,7 +3740,7 @@
       <c r="U46" s="29" t="n"/>
       <c r="V46" s="29" t="inlineStr">
         <is>
-          <t>../../../inputs/user/name</t>
+          <t>false()</t>
         </is>
       </c>
       <c r="W46" s="29" t="n"/>
@@ -3849,14 +3769,10 @@
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>created_by_person_uuid</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
       <c r="C47" s="29" t="n"/>
       <c r="D47" s="29" t="n"/>
       <c r="E47" s="29" t="n"/>
@@ -3876,11 +3792,7 @@
       <c r="S47" s="29" t="n"/>
       <c r="T47" s="29" t="n"/>
       <c r="U47" s="29" t="n"/>
-      <c r="V47" s="29" t="inlineStr">
-        <is>
-          <t>../../../inputs/user/contact_id</t>
-        </is>
-      </c>
+      <c r="V47" s="29" t="n"/>
       <c r="W47" s="29" t="n"/>
       <c r="X47" s="29" t="n"/>
       <c r="Y47" s="29" t="n"/>
@@ -3907,24 +3819,52 @@
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>created_by_place_uuid</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="n"/>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="29" t="n"/>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H48" s="29" t="n"/>
-      <c r="I48" s="29" t="n"/>
+      <c r="I48" s="29" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="J48" s="29" t="n"/>
       <c r="K48" s="29" t="n"/>
-      <c r="L48" s="29" t="n"/>
+      <c r="L48" s="29" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
       <c r="M48" s="29" t="n"/>
       <c r="N48" s="29" t="n"/>
       <c r="O48" s="29" t="n"/>
@@ -3934,11 +3874,7 @@
       <c r="S48" s="29" t="n"/>
       <c r="T48" s="29" t="n"/>
       <c r="U48" s="29" t="n"/>
-      <c r="V48" s="29" t="inlineStr">
-        <is>
-          <t>../../../inputs/user/facility_id</t>
-        </is>
-      </c>
+      <c r="V48" s="29" t="n"/>
       <c r="W48" s="29" t="n"/>
       <c r="X48" s="29" t="n"/>
       <c r="Y48" s="29" t="n"/>
@@ -3965,10 +3901,14 @@
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="n"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
       <c r="C49" s="29" t="n"/>
       <c r="D49" s="29" t="n"/>
       <c r="E49" s="29" t="n"/>
@@ -3988,7 +3928,11 @@
       <c r="S49" s="29" t="n"/>
       <c r="T49" s="29" t="n"/>
       <c r="U49" s="29" t="n"/>
-      <c r="V49" s="29" t="n"/>
+      <c r="V49" s="29" t="inlineStr">
+        <is>
+          <t>../../../inputs/user/name</t>
+        </is>
+      </c>
       <c r="W49" s="29" t="n"/>
       <c r="X49" s="29" t="n"/>
       <c r="Y49" s="29" t="n"/>
@@ -4015,10 +3959,14 @@
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="n"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>created_by_person_uuid</t>
+        </is>
+      </c>
       <c r="C50" s="29" t="n"/>
       <c r="D50" s="29" t="n"/>
       <c r="E50" s="29" t="n"/>
@@ -4038,7 +3986,11 @@
       <c r="S50" s="29" t="n"/>
       <c r="T50" s="29" t="n"/>
       <c r="U50" s="29" t="n"/>
-      <c r="V50" s="29" t="n"/>
+      <c r="V50" s="29" t="inlineStr">
+        <is>
+          <t>../../../inputs/user/contact_id</t>
+        </is>
+      </c>
       <c r="W50" s="29" t="n"/>
       <c r="X50" s="29" t="n"/>
       <c r="Y50" s="29" t="n"/>
@@ -4062,6 +4014,164 @@
       <c r="AQ50" s="29" t="n"/>
       <c r="AR50" s="29" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>created_by_place_uuid</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="29" t="n"/>
+      <c r="I51" s="29" t="n"/>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="29" t="n"/>
+      <c r="L51" s="29" t="n"/>
+      <c r="M51" s="29" t="n"/>
+      <c r="N51" s="29" t="n"/>
+      <c r="O51" s="29" t="n"/>
+      <c r="P51" s="29" t="n"/>
+      <c r="Q51" s="29" t="n"/>
+      <c r="R51" s="29" t="n"/>
+      <c r="S51" s="29" t="n"/>
+      <c r="T51" s="29" t="n"/>
+      <c r="U51" s="29" t="n"/>
+      <c r="V51" s="29" t="inlineStr">
+        <is>
+          <t>../../../inputs/user/facility_id</t>
+        </is>
+      </c>
+      <c r="W51" s="29" t="n"/>
+      <c r="X51" s="29" t="n"/>
+      <c r="Y51" s="29" t="n"/>
+      <c r="Z51" s="29" t="n"/>
+      <c r="AA51" s="29" t="n"/>
+      <c r="AB51" s="29" t="n"/>
+      <c r="AC51" s="29" t="n"/>
+      <c r="AD51" s="29" t="n"/>
+      <c r="AE51" s="29" t="n"/>
+      <c r="AF51" s="29" t="n"/>
+      <c r="AG51" s="29" t="n"/>
+      <c r="AH51" s="29" t="n"/>
+      <c r="AI51" s="29" t="n"/>
+      <c r="AJ51" s="29" t="n"/>
+      <c r="AK51" s="29" t="n"/>
+      <c r="AL51" s="29" t="n"/>
+      <c r="AM51" s="29" t="n"/>
+      <c r="AN51" s="29" t="n"/>
+      <c r="AO51" s="29" t="n"/>
+      <c r="AP51" s="29" t="n"/>
+      <c r="AQ51" s="29" t="n"/>
+      <c r="AR51" s="29" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="29" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="29" t="n"/>
+      <c r="G52" s="29" t="n"/>
+      <c r="H52" s="29" t="n"/>
+      <c r="I52" s="29" t="n"/>
+      <c r="J52" s="29" t="n"/>
+      <c r="K52" s="29" t="n"/>
+      <c r="L52" s="29" t="n"/>
+      <c r="M52" s="29" t="n"/>
+      <c r="N52" s="29" t="n"/>
+      <c r="O52" s="29" t="n"/>
+      <c r="P52" s="29" t="n"/>
+      <c r="Q52" s="29" t="n"/>
+      <c r="R52" s="29" t="n"/>
+      <c r="S52" s="29" t="n"/>
+      <c r="T52" s="29" t="n"/>
+      <c r="U52" s="29" t="n"/>
+      <c r="V52" s="29" t="n"/>
+      <c r="W52" s="29" t="n"/>
+      <c r="X52" s="29" t="n"/>
+      <c r="Y52" s="29" t="n"/>
+      <c r="Z52" s="29" t="n"/>
+      <c r="AA52" s="29" t="n"/>
+      <c r="AB52" s="29" t="n"/>
+      <c r="AC52" s="29" t="n"/>
+      <c r="AD52" s="29" t="n"/>
+      <c r="AE52" s="29" t="n"/>
+      <c r="AF52" s="29" t="n"/>
+      <c r="AG52" s="29" t="n"/>
+      <c r="AH52" s="29" t="n"/>
+      <c r="AI52" s="29" t="n"/>
+      <c r="AJ52" s="29" t="n"/>
+      <c r="AK52" s="29" t="n"/>
+      <c r="AL52" s="29" t="n"/>
+      <c r="AM52" s="29" t="n"/>
+      <c r="AN52" s="29" t="n"/>
+      <c r="AO52" s="29" t="n"/>
+      <c r="AP52" s="29" t="n"/>
+      <c r="AQ52" s="29" t="n"/>
+      <c r="AR52" s="29" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="29" t="n"/>
+      <c r="D53" s="29" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="29" t="n"/>
+      <c r="G53" s="29" t="n"/>
+      <c r="H53" s="29" t="n"/>
+      <c r="I53" s="29" t="n"/>
+      <c r="J53" s="29" t="n"/>
+      <c r="K53" s="29" t="n"/>
+      <c r="L53" s="29" t="n"/>
+      <c r="M53" s="29" t="n"/>
+      <c r="N53" s="29" t="n"/>
+      <c r="O53" s="29" t="n"/>
+      <c r="P53" s="29" t="n"/>
+      <c r="Q53" s="29" t="n"/>
+      <c r="R53" s="29" t="n"/>
+      <c r="S53" s="29" t="n"/>
+      <c r="T53" s="29" t="n"/>
+      <c r="U53" s="29" t="n"/>
+      <c r="V53" s="29" t="n"/>
+      <c r="W53" s="29" t="n"/>
+      <c r="X53" s="29" t="n"/>
+      <c r="Y53" s="29" t="n"/>
+      <c r="Z53" s="29" t="n"/>
+      <c r="AA53" s="29" t="n"/>
+      <c r="AB53" s="29" t="n"/>
+      <c r="AC53" s="29" t="n"/>
+      <c r="AD53" s="29" t="n"/>
+      <c r="AE53" s="29" t="n"/>
+      <c r="AF53" s="29" t="n"/>
+      <c r="AG53" s="29" t="n"/>
+      <c r="AH53" s="29" t="n"/>
+      <c r="AI53" s="29" t="n"/>
+      <c r="AJ53" s="29" t="n"/>
+      <c r="AK53" s="29" t="n"/>
+      <c r="AL53" s="29" t="n"/>
+      <c r="AM53" s="29" t="n"/>
+      <c r="AN53" s="29" t="n"/>
+      <c r="AO53" s="29" t="n"/>
+      <c r="AP53" s="29" t="n"/>
+      <c r="AQ53" s="29" t="n"/>
+      <c r="AR53" s="29" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
   <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -4074,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.109375" customWidth="1" min="1" max="1"/>
@@ -4136,6 +4246,11 @@
           <t>label::fr</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>creator_role</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -4479,6 +4594,11 @@
           <t>ASHA</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cho anm mpw nurse physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -4521,6 +4641,11 @@
           <t>ANM</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cho anm mpw nurse physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -4563,6 +4688,11 @@
           <t>MPW</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cho anm mpw nurse physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -4605,6 +4735,11 @@
           <t>CHO</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>nurse physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -4647,6 +4782,11 @@
           <t>Infirmier</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -4689,6 +4829,11 @@
           <t>Officier Médical</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -4731,6 +4876,11 @@
           <t>Médecin</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -4773,6 +4923,11 @@
           <t>Patient</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>asha cho anm mpw nurse physician medical_officer</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -4813,6 +4968,11 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>Autre</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>asha cho anm mpw nurse physician medical_officer</t>
         </is>
       </c>
     </row>
